--- a/consolidado_horarios.xlsx
+++ b/consolidado_horarios.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Arthur Melo Gusmão" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Diêgo de Araujo Correia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Erasmo da Silva Sà Junior" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Erick Mascarenhas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Erick de Lima Mascarenhas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Hércules Porfirio" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Ian Tenório" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Jadiel Henrique" sheetId="7" state="visible" r:id="rId7"/>
@@ -22,7 +22,7 @@
     <sheet name="Kauã Lessa" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Laura Mainero" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Leandro Wanderley" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Ludson Almeida" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Ludson Lira de Almeida" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Luiz Bomfim" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Luiz Henrique Lima Leite" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Marcela Rocha Silva" sheetId="19" state="visible" r:id="rId19"/>
@@ -4098,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4109,87 +4109,297 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Sáb</t>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 - 08:20---------------
-08:20 - 09:10---------------
-09:20 - 10:10ECOM032ECOM031ECOM032ECOM031---
-10:10 - 11:00ECOM032ECOM031ECOM032ECOM031---
-11:10 - 12:00ECOM027COMP381---ECOM027COMP381
-12:00 - 12:50ECOM027COMP381---ECOM027COMP381
-13:30 - 14:20COMP376COMP399COMP376COMP399---
-14:20 - 15:10COMP376COMP399COMP376COMP399---
-15:20 - 16:10---------------
-16:10 - 17:00---------------
-17:10 - 18:00---------------
-18:00 - 18:50---------------
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>---
----
----
----
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4698,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4709,177 +4919,426 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Sáb</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 15</t>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 - 08:20---------------
-08:20 - 09:10---------------
-09:20 - 10:10------ECOM015ECOM019ECOM019
-10:10 - 11:00------ECOM015ECOM019ECOM019
-11:10 - 12:00------ECOM015------
-12:00 - 12:50------ECOM015------
-13:30 - 14:20ECOM020---ECOM020------
-14:20 - 15:10ECOM020---ECOM020------
-15:20 - 16:10---------------
-16:10 - 17:00---------------
-17:10 - 18:00---------ECOM023ECOM023
-18:00 - 18:50---------ECOM023ECOM023
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>---
----
----
----
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>17:10 -
+18:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18:00 -
+18:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9412,7 +9871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9423,87 +9882,383 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Sáb</t>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 - 08:20---------------
-08:20 - 09:10---------------
-09:20 - 10:10------------ECOM046
-10:10 - 11:00------------ECOM046
-11:10 - 12:00------------ECOM046
-12:00 - 12:50------------ECOM046
-13:30 - 14:20---COMP399---COMP399---
-14:20 - 15:10---COMP399---COMP399---
-15:20 - 16:10---------------
-16:10 - 17:00---------------
-17:10 - 18:00---------COMP384---
-18:00 - 18:50---------COMP384---
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>---
----
-COMP385
-COMP385
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ECOM046</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>COMP385</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ECOM046</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMP385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ECOM046</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ECOM046</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>17:10 -
+18:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMP384</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18:00 -
+18:50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMP384</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9830,7 +10585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9841,165 +10596,440 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sáb</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 - 08:20---------------
-08:20 - 09:10---------------
-09:20 - 10:10ECOM032ECOM031ECOM032ECOM031---
-10:10 - 11:00ECOM032ECOM031ECOM032ECOM031---
-11:10 - 12:00COMP379COMP381COMP379---COMP381
-12:00 - 12:50COMP379COMP381COMP379---COMP381
-13:30 - 14:20---COMP399---COMP399---
-14:20 - 15:10---COMP399---COMP399COMP383
-15:20 - 16:10------------COMP383
-16:10 - 17:00---------------
-17:10 - 18:00COMP390---COMP390------
-18:00 - 18:50COMP390---COMP390------
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>---
----
----
----
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ECOM032</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMP379</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COMP379</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMP379</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMP379</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>COMP381</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMP399</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMP383</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COMP383</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>17:10 -
+18:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMP390</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMP390</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18:00 -
+18:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COMP390</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMP390</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11641,176 +12671,480 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horários</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Discente:</t>
+          <t>Dom</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>WALTER SOARES COSTA NETO</t>
+          <t>Seg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Horários</t>
+          <t>Ter</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Seg</t>
+          <t>Qua</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ter</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Qua</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Sáb</t>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>07:30 -
+08:20</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Curso:</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CIÊNCIA DA COMPUTAÇÃO - CAMPUS MACEIÓ - MATUTINO E VESPERTINO - Maceió -
-BACHARELADO - Presencial - MT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>08:20 -
+09:10</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Status:</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09:20 -
+10:10</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tipo:</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>07:30 - 08:20COMP387------------
-08:20 - 09:10COMP387------------
-09:20 - 10:10COMP387------------
-10:10 - 11:00COMP387------------
-11:10 - 12:00ECOM027------ECOM027---
-12:00 - 12:50ECOM027------ECOM027---
-13:30 - 14:20COMP376COMP372COMP376COMP372COMP377
-14:20 - 15:10COMP376COMP372COMP376COMP372COMP377
-15:20 - 16:10---COMP373---COMP373---
-16:10 - 17:00---COMP373---COMP373---
-17:10 - 18:00---------------
-18:00 - 18:50---------------
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>---</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>---
----
----
----
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16:10 -
+17:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15027,7 +16361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15038,87 +16372,396 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sáb</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sab</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 - 08:20---------------
-08:20 - 09:10---------------
-09:20 - 10:10ECOM059ECOM031ECOM059ECOM031---
-10:10 - 11:00ECOM059ECOM031ECOM059ECOM031---
-11:10 - 12:00ECOM027------ECOM027---
-12:00 - 12:50ECOM027------ECOM027---
-13:30 - 14:20COMP376COMP372COMP376COMP372COMP377
-14:20 - 15:10COMP376COMP372COMP376COMP372COMP377
-15:20 - 16:10---COMP373---COMP373---
-16:10 - 17:00---COMP373---COMP373---
-17:10 - 18:00---------------
-18:00 - 18:50---------------
-19:00 - 19:50---------------
-19:50 - 20:40---------------
-20:50 - 21:40---------------
-21:40 - 22:30---------------</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>---
----
----
----
----
----
----
----
----
----
----
----
----
----
----
----</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ECOM059</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ECOM059</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ECOM059</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ECOM059</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ECOM031</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 -
+12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 -
+12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:10 -
+17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidado_horarios.xlsx
+++ b/consolidado_horarios.xlsx
@@ -11,31 +11,31 @@
     <sheet name="Diêgo de Araujo Correia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Erasmo da Silva Sà Junior" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Erick de Lima Mascarenhas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Hércules Porfirio" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ian Tenório" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Jadiel Henrique" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="JOSE WENDER FERREIRA DUARTE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="José Riquelme Teixeira da Silv" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="João Pedro" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="JULIA AZEVEDO PEREIRA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Julia Gonçalves" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Kauã Lessa" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Laura Mainero" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leandro Wanderley" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Hércules Porfirio de Jesus San" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ian Carlos Cidreira Tenório" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Jadiel Henrique Calado Lino" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="José Riquelme Teixeira da Silv" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="José Wender Ferreira Duarte" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="João Pedro Simões da Silva Sou" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Julia Azevedo Pereira" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Julia Gonçalves dos Santos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Kauã Lessa Lima dos Santos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Laura Beatriz Lins Ramos Maine" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leandro Wanderley Quintela Ten" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Ludson Lira de Almeida" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Luiz Bomfim" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Luiz Henrique Lima Leite" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Luiz Henrique Lima Leite" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Luiz Miguel de Melo Bomfim" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Marcela Rocha Silva" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Matheus Almeida Souza" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Neilton Gabriel Goncalves" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="PEDRO ANDRE DA SILVA NETO" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Pedro André da Silva Neto" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Pedro Henrique Feliciano da Si" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="PEDRO HENRIQUE OLIVEIRA NEVES" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Raul Alves" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Pedro Henrique Oliveira Neves" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Raul Alves do Nascimento" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="Victor Moura Amaral de Oliveir" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="WALTER SOARES COSTA NETO" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Wyvian Valença" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="YURI RAPHAEL MOTA DE ARAÚJO BA" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Walter Soares Costa Neto" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Wyvian Gabrielly Cavalcante VV" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Yuri Raphael Mota de Araújo Ba" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="Érico Almeida Bernardino" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
@@ -4412,7 +4412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4423,75 +4423,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Dom</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 1</t>
+          <t>Seg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Dom</t>
+          <t>Ter</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Seg</t>
+          <t>Qua</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Ter</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Qua</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -4500,7 +4460,8 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 - 10:10</t>
+          <t>09:20 -
+10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4513,44 +4474,37 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ECOM015</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>COMP385</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 - 11:00</t>
+          <t>10:10 -
+11:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4563,44 +4517,37 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ECOM019</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ECOM015</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>COMP385</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+          <t>ECOM019</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 - 12:00</t>
+          <t>11:10 -
+12:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4610,38 +4557,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECOM027</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ECOM015</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ECOM027</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -4650,7 +4589,8 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 - 12:50</t>
+          <t>12:00 -
+12:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4660,38 +4600,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECOM027</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ECOM015</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ECOM015</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ECOM027</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -4700,107 +4632,94 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 - 14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 - 15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:20 - 16:10</t>
+          <t>15:20 -
+16:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4810,47 +4729,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ECOM179</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALE0002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ECOM179</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:10 - 17:00</t>
+          <t>17:10 -
+18:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4860,42 +4772,77 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ECOM179</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ECOM179</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18:00 -
+18:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4908,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4919,35 +4866,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -4956,8 +4943,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
+          <t>09:20 - 10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4970,37 +4956,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ECOM019</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ECOM019</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>COMP385</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
+          <t>10:10 - 11:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5013,37 +5006,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ECOM019</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ECOM019</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>COMP385</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
+          <t>11:10 - 12:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5053,30 +5053,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -5085,8 +5093,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
+          <t>12:00 - 12:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5096,30 +5103,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ECOM027</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -5128,94 +5143,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FALE0002</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FALE0002</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
+          <t>15:20 - 16:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5225,40 +5253,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FALE0002</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>ECOM179</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ECOM179</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:10 -
-18:00</t>
+          <t>16:10 - 17:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5268,77 +5303,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
+          <t>ECOM179</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>18:00 -
-18:50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ECOM179</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17868,6 +17868,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horários</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Sab</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>09:20 - 10:10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 - 11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 - 12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 - 12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>COMP383</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>COMP383</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -19573,500 +20069,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Horários</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dom</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Seg</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ter</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Qua</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Sab</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>09:20 - 10:10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10:10 - 11:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>11:10 - 12:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>12:00 - 12:50</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>13:30 - 14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>14:20 - 15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15:20 - 16:10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>16:10 - 17:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/consolidado_horarios.xlsx
+++ b/consolidado_horarios.xlsx
@@ -11,31 +11,31 @@
     <sheet name="Diêgo de Araujo Correia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Erasmo da Silva Sà Junior" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Erick de Lima Mascarenhas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Hércules Porfirio" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ian Tenório" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Jadiel Henrique" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="JOSE WENDER FERREIRA DUARTE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="José Riquelme Teixeira da Silv" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="João Pedro" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Hércules Porfirio de Jesus San" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ian Carlos Cidreira Tenório" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Jadiel Henrique Calado Lino" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="José Riquelme Teixeira da Silv" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="José Wender Ferreira Duarte" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="João Pedro Simões da Silva Sou" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="JULIA AZEVEDO PEREIRA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Julia Gonçalves" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Kauã Lessa" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Laura Mainero" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leandro Wanderley" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Julia Gonçalves dos Santos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Kauã Lessa Lima dos Santos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Laura Beatriz Lins Ramos Maine" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leandro Wanderley Quintela Ten" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Ludson Lira de Almeida" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Luiz Bomfim" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Luiz Henrique Lima Leite" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Luiz Henrique Lima Leite" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Luiz Miguel de Melo Bomfim" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Marcela Rocha Silva" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Matheus Almeida Souza" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Neilton Gabriel Goncalves" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="PEDRO ANDRE DA SILVA NETO" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Pedro André da Silva Neto" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Pedro Henrique Feliciano da Si" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="PEDRO HENRIQUE OLIVEIRA NEVES" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Raul Alves" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Raul Alves do Nascimento" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="Victor Moura Amaral de Oliveir" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="WALTER SOARES COSTA NETO" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Wyvian Gabrielly Cavalcante Va" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="YURI RAPHAEL MOTA DE ARAÚJO BA" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Wyvian Gabrielly Cavalcante VV" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Yuri Raphael Mota de Araújo Ba" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="Érico Almeida Bernardino" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
@@ -4246,7 +4246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM019</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM019</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>COMP385</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -4363,17 +4363,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM019</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM019</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>COMP385</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECOM027</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ECOM027</t>
+          <t>---</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECOM027</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ECOM027</t>
+          <t>---</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4477,17 +4477,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>COMP376</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>FALE0002</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COMP376</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMP377</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4520,17 +4520,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>COMP376</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>FALE0002</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COMP376</t>
+          <t>ECOM020</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMP377</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ECOM179</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>FALE0002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ECOM179</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4595,8 +4595,8 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
+          <t>17:10 -
+18:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ECOM179</t>
+          <t>---</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4621,15 +4621,58 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM023</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ECOM179</t>
+          <t>ECOM023</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18:00 -
+18:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ECOM023</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -4646,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4720,17 +4763,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ECOM019</t>
+          <t>---</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ECOM019</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>COMP385</t>
         </is>
       </c>
     </row>
@@ -4763,17 +4806,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ECOM019</t>
+          <t>---</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ECOM019</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>COMP385</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4834,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM027</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4806,7 +4849,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM027</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4834,7 +4877,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM027</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4849,7 +4892,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM027</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4877,17 +4920,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>COMP376</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FALE0002</t>
+          <t>---</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>COMP376</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4897,7 +4940,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>COMP377</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4920,17 +4963,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>COMP376</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FALE0002</t>
+          <t>---</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECOM020</t>
+          <t>COMP376</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4940,7 +4983,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>COMP377</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4963,12 +5006,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM179</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FALE0002</t>
+          <t>---</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4983,7 +5026,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM179</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4995,8 +5038,8 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:10 -
-18:00</t>
+          <t>16:10 -
+17:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5006,7 +5049,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>ECOM179</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5021,58 +5064,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ECOM023</t>
+          <t>---</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ECOM023</t>
+          <t>ECOM179</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>18:00 -
-18:50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ECOM023</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -15897,1407 +15897,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Horários</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Dom</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Seg</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Ter</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Qua</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sab</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E23/08/2025 15:29
-AM
-Período Letivo:2025.1 (07/07/2025 à 19/11/2025)Nível:GRADUAÇÃO
-Matrícula:23210792Vínculo:REGULAR
-Nome:JOSE WENDER FERREIRA DUARTE
-CIÊNCIA DA COMPUTAÇÃO - CAMPUS MACEIÓ - MATUTINO E VESPERTINO -
-Curso:
-PRESENCIAL - Maceió - BACHARELADO - Regular - Semestral (13216) - MT
-TM: 5
-AM: 1
-Cód.Componentes Curriculares/DocentesTurma NívelStatusHorário
-COMP377 ACE 1: PROJETO I
-014
-MATRICULADO6T12 (07/07/2025 -
-ROBERTA VILHENA VIEIRA LOPES19/11/2025)
-Tipo: ATIVIDADELocal: Instituto de Computação
-COMP395 INTERAÇÃO HOMEM-MÁQUINA
-01-
-MATRICULADO24T34
-FABIO PARAGUACU DUARTE DA COSTA
-Tipo: DISCIPLINALocal: Instituto de
-Computação
-COMP387 NOÇÕES DE DIREITO
-017
-MATRICULADO2M1234
-CID CAVALCANTI DE ALBUQUERQUE
-Tipo: DISCIPLINALocal: Instituto de
-Computaçãp
-COMP372 PROGRAMAÇÃO 2
-014
-MATRICULADO35T12
-MARIO HOZANO LUCAS DE SOUZA
-Tipo: DISCIPLINALocal: Instituto de
-Computação
-COMP373 PROGRAMAÇÃO 3
-014
-MATRICULADO35T34
-RANILSON OSCAR ARAUJO PAIVA
-Tipo: DISCIPLINALocal: Instituto de
-Computação
-COMP376 TEORIA DA COMPUTAÇÃO
-014
-MATRICULADO24T12
-FABIO PARAGUACU DUARTE DA COSTA
-Tipo: DISCIPLINALocal: Instituto de
-Computação
-TH:
-HoráriosDomSegTerQuaQuiSexSab
-07:30 -
----COMP387---------------
-08:20
-08:20 -
----COMP387---------------
-09:10
-09:20 -
----COMP387---------------
-10:10
-10:10 -
----COMP387---------------
-11:00
-13:30 -
----COMP376COMP372COMP376COMP372COMP377---
-14:20
-14:20 -
----COMP376COMP372COMP376COMP372COMP377---
-15:10
-15:20 -
----COMP395COMP373COMP395COMP373------
-16:10
-16:10 -
----COMP395COMP373COMP395COMP373------
-17:00</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>07:30 -
-08:20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>08:20 -
-09:10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>09:20 -
-10:10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10:10 -
-11:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E23/08/2025 15:29</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E23/08/2025 15:29</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Cód.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Componentes Curriculares/Docentes</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Turma</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Nível</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Horário</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ACE 1: PROJETO I
-ROBERTA VILHENA VIEIRA LOPES
-Tipo: ATIVIDADELocal: Instituto de Computação</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>6T12 (07/07/2025 -
-19/11/2025)</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>INTERAÇÃO HOMEM-MÁQUINA
-FABIO PARAGUACU DUARTE DA COSTA
-Tipo: DISCIPLINALocal: Instituto de
-Computação</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>24T34</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NOÇÕES DE DIREITO
-CID CAVALCANTI DE ALBUQUERQUE
-Tipo: DISCIPLINALocal: Instituto de
-Computaçãp</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2M1234</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>PROGRAMAÇÃO 2
-MARIO HOZANO LUCAS DE SOUZA
-Tipo: DISCIPLINALocal: Instituto de
-Computação</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>35T12</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>PROGRAMAÇÃO 3
-RANILSON OSCAR ARAUJO PAIVA
-Tipo: DISCIPLINALocal: Instituto de
-Computação</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>35T34</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TEORIA DA COMPUTAÇÃO
-FABIO PARAGUACU DUARTE DA COSTA
-Tipo: DISCIPLINALocal: Instituto de
-Computação</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>24T12</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Horários</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Dom</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Seg</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ter</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Qua</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Sab</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>07:30 -
-08:20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>08:20 -
-09:10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>09:20 -
-10:10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10:10 -
-11:00</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>COMP387</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>COMP376</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>COMP372</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>COMP377</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>COMP395</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>COMP373</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -18736,4 +17335,1405 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horários</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sab</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>UFA
+SIGA
+A
+Portal do Discente
+E23/08/2025 15:29
+AM
+Período Letivo:2025.1 (07/07/2025 à 19/11/2025)Nível:GRADUAÇÃO
+Matrícula:23210792Vínculo:REGULAR
+Nome:JOSE WENDER FERREIRA DUARTE
+CIÊNCIA DA COMPUTAÇÃO - CAMPUS MACEIÓ - MATUTINO E VESPERTINO -
+Curso:
+PRESENCIAL - Maceió - BACHARELADO - Regular - Semestral (13216) - MT
+TM: 5
+AM: 1
+Cód.Componentes Curriculares/DocentesTurma NívelStatusHorário
+COMP377 ACE 1: PROJETO I
+014
+MATRICULADO6T12 (07/07/2025 -
+ROBERTA VILHENA VIEIRA LOPES19/11/2025)
+Tipo: ATIVIDADELocal: Instituto de Computação
+COMP395 INTERAÇÃO HOMEM-MÁQUINA
+01-
+MATRICULADO24T34
+FABIO PARAGUACU DUARTE DA COSTA
+Tipo: DISCIPLINALocal: Instituto de
+Computação
+COMP387 NOÇÕES DE DIREITO
+017
+MATRICULADO2M1234
+CID CAVALCANTI DE ALBUQUERQUE
+Tipo: DISCIPLINALocal: Instituto de
+Computaçãp
+COMP372 PROGRAMAÇÃO 2
+014
+MATRICULADO35T12
+MARIO HOZANO LUCAS DE SOUZA
+Tipo: DISCIPLINALocal: Instituto de
+Computação
+COMP373 PROGRAMAÇÃO 3
+014
+MATRICULADO35T34
+RANILSON OSCAR ARAUJO PAIVA
+Tipo: DISCIPLINALocal: Instituto de
+Computação
+COMP376 TEORIA DA COMPUTAÇÃO
+014
+MATRICULADO24T12
+FABIO PARAGUACU DUARTE DA COSTA
+Tipo: DISCIPLINALocal: Instituto de
+Computação
+TH:
+HoráriosDomSegTerQuaQuiSexSab
+07:30 -
+---COMP387---------------
+08:20
+08:20 -
+---COMP387---------------
+09:10
+09:20 -
+---COMP387---------------
+10:10
+10:10 -
+---COMP387---------------
+11:00
+13:30 -
+---COMP376COMP372COMP376COMP372COMP377---
+14:20
+14:20 -
+---COMP376COMP372COMP376COMP372COMP377---
+15:10
+15:20 -
+---COMP395COMP373COMP395COMP373------
+16:10
+16:10 -
+---COMP395COMP373COMP395COMP373------
+17:00</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>07:30 -
+08:20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>08:20 -
+09:10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09:20 -
+10:10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:10 -
+17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UFA
+SIGA
+A
+Portal do Discente
+E23/08/2025 15:29</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UFA
+SIGA
+A
+Portal do Discente
+E23/08/2025 15:29</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cód.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Componentes Curriculares/Docentes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Turma</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ACE 1: PROJETO I
+ROBERTA VILHENA VIEIRA LOPES
+Tipo: ATIVIDADELocal: Instituto de Computação</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6T12 (07/07/2025 -
+19/11/2025)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>INTERAÇÃO HOMEM-MÁQUINA
+FABIO PARAGUACU DUARTE DA COSTA
+Tipo: DISCIPLINALocal: Instituto de
+Computação</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>24T34</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NOÇÕES DE DIREITO
+CID CAVALCANTI DE ALBUQUERQUE
+Tipo: DISCIPLINALocal: Instituto de
+Computaçãp</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2M1234</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PROGRAMAÇÃO 2
+MARIO HOZANO LUCAS DE SOUZA
+Tipo: DISCIPLINALocal: Instituto de
+Computação</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>35T12</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PROGRAMAÇÃO 3
+RANILSON OSCAR ARAUJO PAIVA
+Tipo: DISCIPLINALocal: Instituto de
+Computação</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>35T34</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TEORIA DA COMPUTAÇÃO
+FABIO PARAGUACU DUARTE DA COSTA
+Tipo: DISCIPLINALocal: Instituto de
+Computação</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MATRICULADO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>24T12</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Horários</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sab</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>07:30 -
+08:20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>08:20 -
+09:10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>09:20 -
+10:10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10:10 -
+11:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>COMP387</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13:30 -
+14:20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>14:20 -
+15:10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>COMP376</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>COMP372</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>COMP377</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15:20 -
+16:10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16:10 -
+17:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>COMP395</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>COMP373</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/consolidado_horarios.xlsx
+++ b/consolidado_horarios.xlsx
@@ -17,7 +17,7 @@
     <sheet name="José Riquelme Teixeira da Silv" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="José Wender Ferreira Duarte" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="João Pedro Simões da Silva Sou" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="JULIA AZEVEDO PEREIRA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Julia Azevedo Pereira" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Julia Gonçalves dos Santos" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Kauã Lessa Lima dos Santos" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Laura Beatriz Lins Ramos Maine" sheetId="14" state="visible" r:id="rId14"/>
@@ -30,10 +30,10 @@
     <sheet name="Neilton Gabriel Goncalves" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Pedro André da Silva Neto" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Pedro Henrique Feliciano da Si" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="PEDRO HENRIQUE OLIVEIRA NEVES" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Pedro Henrique Oliveira Neves" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="Raul Alves do Nascimento" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="Victor Moura Amaral de Oliveir" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="WALTER SOARES COSTA NETO" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Walter Soares Costa Neto" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="Wyvian Gabrielly Cavalcante VV" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Yuri Raphael Mota de Araújo Ba" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="Érico Almeida Bernardino" sheetId="30" state="visible" r:id="rId30"/>
@@ -2246,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2257,35 +2257,70 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -2294,432 +2329,492 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07:30 -
-08:20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>07:30 - 08:20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ECOM028</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>ECOM028</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08:20 -
-09:10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>08:20 - 09:10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>ECOM028</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>ECOM028</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>11:10 - 12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>12:00 - 12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>ECIV026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>ECIV026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>ECIV026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>ECIV026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>IF0003</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>IF0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>IF0003</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>IF0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17:10 -
-18:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>17:10 - 18:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>ECOM048</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18:00 -
-18:50</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>18:00 - 18:50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>ECOM048</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3618,7 +3713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3629,35 +3724,70 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -3666,260 +3796,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>09:20 - 10:10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>ECOM032</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>ECOM032</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>10:10 - 11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>ECOM032</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>ECOM032</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>COMP395</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>COMP395</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>COMP395</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>COMP395</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:10 -
-18:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>17:10 - 18:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>COMP390</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>COMP390</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:00 -
-18:50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>18:00 - 18:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>COMP390</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>COMP390</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4689,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,35 +4866,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -4737,8 +4943,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
+          <t>09:20 - 10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4751,37 +4956,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
+          <t>10:10 - 11:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4794,37 +5006,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
+          <t>11:10 - 12:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4837,27 +5056,35 @@
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -4866,8 +5093,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
+          <t>12:00 - 12:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4880,27 +5106,35 @@
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -4909,94 +5143,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
+          <t>15:20 - 16:10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5009,37 +5256,44 @@
           <t>ECOM179</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>ECOM179</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
+          <t>16:10 - 17:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5052,31 +5306,39 @@
           <t>ECOM179</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>ECOM179</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5403,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5414,35 +5676,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
@@ -5451,273 +5763,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>11:10 - 12:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>COMP397</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>COMP397</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>12:00 - 12:50</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>COMP397</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>COMP397</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17:10 -
-18:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>17:10 - 18:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>---</t>
@@ -5728,39 +6089,48 @@
           <t>---</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>COMP384</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18:00 -
-18:50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>18:00 - 18:50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>---</t>
@@ -5771,26 +6141,40 @@
           <t>---</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>COMP382</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>COMP384</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11756,7 +12140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11767,45 +12151,84 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
+          <t>09:20 - 10:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11818,37 +12241,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>ECOM031</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>ECOM031</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
+          <t>10:10 - 11:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11861,37 +12291,44 @@
           <t>---</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>ECOM031</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>ECOM031</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>COMP385</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
+          <t>11:10 - 12:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11904,37 +12341,44 @@
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
+          <t>12:00 - 12:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11947,117 +12391,139 @@
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>ECOM015</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>ECOM027</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12070,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12081,138 +12547,180 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>09:20 - 10:10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>10:10 - 11:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>11:10 - 12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>---</t>
@@ -12220,42 +12728,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12:00 -
-12:50</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>12:00 - 12:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>---</t>
@@ -12263,111 +12777,134 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>---</t>
         </is>
@@ -12376,88 +12913,100 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>ECOM011</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ECOM011</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>ECOM011</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ECOM011</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15572,38 +16121,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>HoráriosDomSegTerQuaQuiSexSab
+09:20 -
+---COMP369------COMP369------
+10:10
+10:10 -
+---COMP369------COMP369------
+11:00
+13:30 -
+---COMP376COMP372COMP376COMP372COMP377---
+14:20
+14:20 -
+---COMP376COMP372COMP376COMP372COMP377---
+15:10
+15:20 -
+------COMP373---COMP373------
+16:10
+16:10 -
+------COMP373---COMP373------
+17:00
+ATENÇÃO
+Para verificar a autenticidade deste documento acesse http://sigaa.sig.ufal.br/sigaa/documentos/
+informando a matrícula, a data de emissão e o código de verificação 4b1d86db3e
+SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
+app-1.srv1inst1 23/08/2025 19:03</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Horários</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qua</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -15625,266 +16197,298 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
+app-1.srv1inst1 23/08/2025 19:03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>09:20 -
 10:10</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>10:10 -
 11:00</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>13:30 -
 14:20</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>COMP372</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>COMP372</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>14:20 -
 15:10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>COMP372</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>COMP376</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>COMP372</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>COMP377</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>15:20 -
 16:10</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>COMP373</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>COMP373</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>16:10 -
 17:00</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>COMP373</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>COMP373</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
+app-1.srv1inst1 23/08/2025 19:03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15897,95 +16501,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E25/09/2025 17:17
-AM
-Período Letivo:2025.1 (07/07/2025 à 19/11/2025)Nível:GRADUAÇÃO
-Matrícula:202407400Vínculo:REGULAR
-Nome:JOSÉ RIQUELME TEIXEIRA DA SILVA
-CIÊNCIA DA COMPUTAÇÃO - CAMPUS MACEIÓ - MATUTINO E VESPERTINO -
-Curso:
-PRESENCIAL - Maceió - BACHARELADO - Regular - Semestral (13216) - MT
-TM: 5
-AM: 1
-Cód.Componentes Curriculares/DocentesTurma NívelStatusHorário
-COMP383ACE 2: CONTINUIDADE DO PROJETO I
-015
-MATRICULADO6T23 (07/07/2025 -
-OLIVAL DE GUSMAO FREITAS JUNIOR19/11/2025)
-Tipo: ATIVIDADELocal: Instituto de Computação
-ECOM011ÁLGEBRA LINEAR
-01-
-MATRICULADO24T34
-ARTURO JIMENEZ LOAIZA
-Tipo: DISCIPLINALocal: Auditório-IC
-COMP389CONCEITOS DE LINGUAGEM DE
-01-
-MATRICULADO35T34
-PROGRAMAÇÃO
-RAFAEL DE AMORIM SILVA
-Tipo: DISCIPLINALocal: Instituto de Computação
-ECOM020PROBABILIDADE E ESTATÍSTICA
-013
-MATRICULADO24T12
-PETRUCIO ANTONIO MEDEIROS BARROS
-Tipo: DISCIPLINALocal: Laboratório-01
-ECOM029REDES DE COMPUTADORES
-013
-MATRICULADO34M56
-ALMIR PEREIRA GUIMARAES
-Tipo: DISCIPLINALocal: Terça(Lab-01);
-Quarta(Sala-03-IC)
-COMP369TEORIA DOS GRAFOS
-013
-MATRICULADO25M34
-RIAN GABRIEL SANTOS PINHEIRO
-Tipo: DISCIPLINALocal: Instituto de Computação
-TH:
-HoráriosDomSegTerQuaQuiSexSab
-09:20 -
----COMP369------COMP369------
-10:10
-10:10 -
----COMP369------COMP369------
-11:00
-11:10 -
-------ECOM029ECOM029---------
-12:00
-12:00 -
-------ECOM029ECOM029---------
-12:50
-13:30 -
----ECOM020---ECOM020---------
-14:20
-14:20 -
----ECOM020---ECOM020---COMP383---
-15:10
-15:20 -
----ECOM011COMP389ECOM011COMP389COMP383---
-16:10
-16:10 -
----ECOM011COMP389ECOM011COMP389------
-17:00
-ATENÇÃO
-Para verificar a autenticidade deste documento acesse http://sigaa.sig.ufal.br/sigaa/documentos/
-informando a matrícula, a data de emissão e o código de verificação 087ca85a3b
-SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
-app-1.srv1inst1 25/09/2025 17:17</t>
+          <t>Horários</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Horários</t>
+          <t>Unnamed: 0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -16005,104 +16532,127 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sab</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 5</t>
+          <t>Unnamed: 6</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 6</t>
+          <t>Unnamed: 7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E25/09/2025 17:17</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+          <t>09:20 - 10:10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>COMP369</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:10 - 11:00</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:20 -
-10:10</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>COMP369</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>---</t>
@@ -16113,35 +16663,38 @@
           <t>---</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>COMP369</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:10 - 12:00</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:10 -
-11:00</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16151,48 +16704,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>ECOM029</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:00 - 12:50</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:10 -
-12:00</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16202,55 +16754,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>ECOM029</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>ECOM029</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>12:00 -
-12:50</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:30 - 14:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>---</t>
@@ -16258,14 +16801,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>---</t>
@@ -16273,1064 +16812,179 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+          <t>ECOM020</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:20 - 15:10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>ECOM020</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>COMP383</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:20 - 16:10</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:20 -
-15:10</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+          <t>ECOM011</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COMP389</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>COMP383</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:10 - 17:00</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:20 -
-16:10</t>
+          <t>---</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>ECOM011</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>ECOM011</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>COMP389</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
-app-1.srv1inst1 25/09/2025 17:17</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UFA
-SIGA
-A
-Portal do Discente
-E25/09/2025 17:17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cód.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Componentes Curriculares/Docentes</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Turma</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Nível</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Horário</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ACE 2: CONTINUIDADE DO PROJETO I
-OLIVAL DE GUSMAO FREITAS JUNIOR
-Tipo: ATIVIDADELocal: Instituto de Computação</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6T23 (07/07/2025 -
-19/11/2025)</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ÁLGEBRA LINEAR
-ARTURO JIMENEZ LOAIZA
-Tipo: DISCIPLINALocal: Auditório-IC</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>24T34</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>CONCEITOS DE LINGUAGEM DE
-PROGRAMAÇÃO
-RAFAEL DE AMORIM SILVA
-Tipo: DISCIPLINALocal: Instituto de Computação</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>35T34</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>PROBABILIDADE E ESTATÍSTICA
-PETRUCIO ANTONIO MEDEIROS BARROS
-Tipo: DISCIPLINALocal: Laboratório-01</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>24T12</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>REDES DE COMPUTADORES
-ALMIR PEREIRA GUIMARAES
-Tipo: DISCIPLINALocal: Terça(Lab-01);
-Quarta(Sala-03-IC)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>34M56</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>TEORIA DOS GRAFOS
-RIAN GABRIEL SANTOS PINHEIRO
-Tipo: DISCIPLINALocal: Instituto de Computação</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>MATRICULADO</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>25M34</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Horários</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Dom</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Seg</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ter</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Qua</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Qui</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Sab</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>09:20 -
-10:10</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10:10 -
-11:00</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>COMP369</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>11:10 -
-12:00</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12:00 -
-12:50</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ECOM029</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>13:30 -
-14:20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>14:20 -
-15:10</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>ECOM020</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>15:20 -
-16:10</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>COMP383</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>16:10 -
-17:00</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>ECOM011</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>COMP389</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SIGAA | NTI - Núcleo de Tecnologia da Informação - (82) 3214-1015 | Copyright © 2006-2025 - UFAL - sig-
-app-1.srv1inst1 25/09/2025 17:17</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
